--- a/research/traditional_assets/database/data/tunisia/tunisia_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/tunisia/tunisia_insurance_general.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0489</v>
+        <v>0.111</v>
       </c>
       <c r="E2">
-        <v>-0.117</v>
+        <v>0.0926</v>
       </c>
       <c r="G2">
-        <v>0.09471933471933472</v>
+        <v>0.05871375251220212</v>
       </c>
       <c r="H2">
-        <v>0.09471933471933472</v>
+        <v>0.05871375251220212</v>
       </c>
       <c r="I2">
-        <v>0.08453222453222453</v>
+        <v>0.1041343669250646</v>
       </c>
       <c r="J2">
-        <v>0.07520641137415331</v>
+        <v>0.08736744492902861</v>
       </c>
       <c r="K2">
-        <v>17.51</v>
+        <v>30.02</v>
       </c>
       <c r="L2">
-        <v>0.07280665280665281</v>
+        <v>0.08619006603502727</v>
       </c>
       <c r="M2">
-        <v>9.99</v>
+        <v>13.5968</v>
       </c>
       <c r="N2">
-        <v>0.05048004042445679</v>
+        <v>0.04008490566037736</v>
       </c>
       <c r="O2">
-        <v>0.5705311250713877</v>
+        <v>0.4529247168554297</v>
       </c>
       <c r="P2">
-        <v>9.99</v>
+        <v>13.5968</v>
       </c>
       <c r="Q2">
-        <v>0.05048004042445679</v>
+        <v>0.04008490566037736</v>
       </c>
       <c r="R2">
-        <v>0.5705311250713877</v>
+        <v>0.4529247168554297</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,31 +636,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>29.19</v>
+        <v>35.69</v>
       </c>
       <c r="V2">
-        <v>0.1474987367357251</v>
+        <v>0.1052181603773585</v>
       </c>
       <c r="W2">
-        <v>0.1568205747553574</v>
+        <v>0.1618263201768693</v>
       </c>
       <c r="X2">
-        <v>0.0970441029214887</v>
+        <v>0.1541982539165212</v>
       </c>
       <c r="Y2">
-        <v>0.05977647183386868</v>
+        <v>0.007628066260348065</v>
       </c>
       <c r="Z2">
-        <v>1.677828938188921</v>
+        <v>1.658832102187487</v>
       </c>
       <c r="AA2">
-        <v>0.2387509666213934</v>
+        <v>0.1952190787239407</v>
       </c>
       <c r="AB2">
-        <v>0.0970441029214887</v>
+        <v>0.1541982539165212</v>
       </c>
       <c r="AC2">
-        <v>0.1417068636999048</v>
+        <v>0.04102082480741947</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -672,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-29.19</v>
+        <v>-35.69</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -681,10 +681,10 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.1730187896390255</v>
+        <v>-0.1175908536786267</v>
       </c>
       <c r="AK2">
-        <v>-0.1810681719496309</v>
+        <v>-0.1582634916411689</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,7 +696,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>-1.211706102117061</v>
+        <v>-2.764523625096824</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Assurances Maghrebia SA (BVMT:ASSMA)</t>
+          <t>BH Assurance (BVMT:BHASS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -715,41 +715,47 @@
           <t>Insurance (General)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.165</v>
+      </c>
+      <c r="E3">
+        <v>0.238</v>
+      </c>
       <c r="G3">
-        <v>0.1654294803817603</v>
+        <v>0.1271910112359551</v>
       </c>
       <c r="H3">
-        <v>0.1654294803817603</v>
+        <v>0.1271910112359551</v>
       </c>
       <c r="I3">
-        <v>0.1792152704135737</v>
+        <v>0.1337078651685393</v>
       </c>
       <c r="J3">
-        <v>0.1396722881674819</v>
+        <v>0.1101789007395578</v>
       </c>
       <c r="K3">
-        <v>10.8</v>
+        <v>4.87</v>
       </c>
       <c r="L3">
-        <v>0.1145281018027572</v>
+        <v>0.109438202247191</v>
       </c>
       <c r="M3">
-        <v>4.49</v>
+        <v>0.981</v>
       </c>
       <c r="N3">
-        <v>0.0449</v>
+        <v>0.02286713286713287</v>
       </c>
       <c r="O3">
-        <v>0.4157407407407407</v>
+        <v>0.2014373716632444</v>
       </c>
       <c r="P3">
-        <v>4.49</v>
+        <v>0.981</v>
       </c>
       <c r="Q3">
-        <v>0.0449</v>
+        <v>0.02286713286713287</v>
       </c>
       <c r="R3">
-        <v>0.4157407407407407</v>
+        <v>0.2014373716632444</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,31 +764,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>9.69</v>
+        <v>19.7</v>
       </c>
       <c r="V3">
-        <v>0.0969</v>
+        <v>0.4592074592074592</v>
       </c>
       <c r="W3">
-        <v>0.2596153846153846</v>
+        <v>0.1940239043824701</v>
       </c>
       <c r="X3">
-        <v>0.0970441029214887</v>
+        <v>0.1541982539165212</v>
       </c>
       <c r="Y3">
-        <v>0.162571281693896</v>
+        <v>0.03982565046594891</v>
       </c>
       <c r="Z3">
-        <v>3.203125</v>
+        <v>7.416666666666667</v>
       </c>
       <c r="AA3">
-        <v>0.4473877980364656</v>
+        <v>0.8171601804850536</v>
       </c>
       <c r="AB3">
-        <v>0.0970441029214887</v>
+        <v>0.1541982539165212</v>
       </c>
       <c r="AC3">
-        <v>0.3503436951149769</v>
+        <v>0.6629619265685324</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -794,7 +800,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-9.69</v>
+        <v>-19.7</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -803,10 +809,10 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.1072970878086591</v>
+        <v>-0.8491379310344828</v>
       </c>
       <c r="AK3">
-        <v>-0.20016525511258</v>
+        <v>-2.897058823529411</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -818,7 +824,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-0.4845</v>
+        <v>-3.213703099510604</v>
       </c>
     </row>
     <row r="4">
@@ -829,124 +835,362 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>Assurances Maghrebia SA (BVMT:ASSMA)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Insurance (General)</t>
+        </is>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0.1697699890470975</v>
+      </c>
+      <c r="J4">
+        <v>0.1287228615583129</v>
+      </c>
+      <c r="K4">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="L4">
+        <v>0.1062431544359255</v>
+      </c>
+      <c r="M4">
+        <v>4.46</v>
+      </c>
+      <c r="N4">
+        <v>0.05492610837438423</v>
+      </c>
+      <c r="O4">
+        <v>0.4597938144329897</v>
+      </c>
+      <c r="P4">
+        <v>4.46</v>
+      </c>
+      <c r="Q4">
+        <v>0.05492610837438423</v>
+      </c>
+      <c r="R4">
+        <v>0.4597938144329897</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>6.67</v>
+      </c>
+      <c r="V4">
+        <v>0.08214285714285714</v>
+      </c>
+      <c r="W4">
+        <v>0.1901960784313725</v>
+      </c>
+      <c r="X4">
+        <v>0.1541982539165212</v>
+      </c>
+      <c r="Y4">
+        <v>0.03599782451485134</v>
+      </c>
+      <c r="Z4">
+        <v>2.213172375342399</v>
+      </c>
+      <c r="AA4">
+        <v>0.2848858812758823</v>
+      </c>
+      <c r="AB4">
+        <v>0.1541982539165212</v>
+      </c>
+      <c r="AC4">
+        <v>0.1306876273593611</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>-6.67</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.08949416342412451</v>
+      </c>
+      <c r="AK4">
+        <v>-0.1257778615877805</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Compagnie d'Assurances et de Réassurances ASTREE (BVMT:AST)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Insurance (General)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.111</v>
+      </c>
+      <c r="E5">
+        <v>0.08710000000000001</v>
+      </c>
+      <c r="G5">
+        <v>0.08974008207934336</v>
+      </c>
+      <c r="H5">
+        <v>0.08974008207934336</v>
+      </c>
+      <c r="I5">
+        <v>0.08946648426812587</v>
+      </c>
+      <c r="J5">
+        <v>0.07207300017577514</v>
+      </c>
+      <c r="K5">
+        <v>7.22</v>
+      </c>
+      <c r="L5">
+        <v>0.0987688098495212</v>
+      </c>
+      <c r="M5">
+        <v>5.43</v>
+      </c>
+      <c r="N5">
+        <v>0.05397614314115308</v>
+      </c>
+      <c r="O5">
+        <v>0.7520775623268698</v>
+      </c>
+      <c r="P5">
+        <v>5.43</v>
+      </c>
+      <c r="Q5">
+        <v>0.05397614314115308</v>
+      </c>
+      <c r="R5">
+        <v>0.7520775623268698</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>4.5</v>
+      </c>
+      <c r="V5">
+        <v>0.04473161033797217</v>
+      </c>
+      <c r="W5">
+        <v>0.133456561922366</v>
+      </c>
+      <c r="X5">
+        <v>0.1541982539165212</v>
+      </c>
+      <c r="Y5">
+        <v>-0.02074169199415521</v>
+      </c>
+      <c r="Z5">
+        <v>1.464518972632928</v>
+      </c>
+      <c r="AA5">
+        <v>0.1055522761719991</v>
+      </c>
+      <c r="AB5">
+        <v>0.1541982539165212</v>
+      </c>
+      <c r="AC5">
+        <v>-0.04864597774452213</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>-4.5</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>-0.04682622268470343</v>
+      </c>
+      <c r="AK5">
+        <v>-0.09761388286334056</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>-0.663716814159292</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>Société Tunisienne d'Assurances et de Réassurances (BVMT:STAR)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Insurance (General)</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.0489</v>
-      </c>
-      <c r="E4">
-        <v>-0.117</v>
-      </c>
-      <c r="G4">
-        <v>0.04911080711354309</v>
-      </c>
-      <c r="H4">
-        <v>0.04911080711354309</v>
-      </c>
-      <c r="I4">
-        <v>0.02346101231190151</v>
-      </c>
-      <c r="J4">
-        <v>0.02346101231190151</v>
-      </c>
-      <c r="K4">
-        <v>6.71</v>
-      </c>
-      <c r="L4">
-        <v>0.04589603283173735</v>
-      </c>
-      <c r="M4">
-        <v>5.5</v>
-      </c>
-      <c r="N4">
-        <v>0.05617977528089887</v>
-      </c>
-      <c r="O4">
-        <v>0.819672131147541</v>
-      </c>
-      <c r="P4">
-        <v>5.5</v>
-      </c>
-      <c r="Q4">
-        <v>0.05617977528089887</v>
-      </c>
-      <c r="R4">
-        <v>0.819672131147541</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>19.5</v>
-      </c>
-      <c r="V4">
-        <v>0.1991828396322778</v>
-      </c>
-      <c r="W4">
-        <v>0.05402576489533011</v>
-      </c>
-      <c r="X4">
-        <v>0.0970441029214887</v>
-      </c>
-      <c r="Y4">
-        <v>-0.04301833802615859</v>
-      </c>
-      <c r="Z4">
-        <v>1.283582089552239</v>
-      </c>
-      <c r="AA4">
-        <v>0.03011413520632134</v>
-      </c>
-      <c r="AB4">
-        <v>0.0970441029214887</v>
-      </c>
-      <c r="AC4">
-        <v>-0.06692996771516736</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>0</v>
-      </c>
-      <c r="AG4">
-        <v>-19.5</v>
-      </c>
-      <c r="AH4">
-        <v>0</v>
-      </c>
-      <c r="AI4">
-        <v>0</v>
-      </c>
-      <c r="AJ4">
-        <v>-0.2487244897959184</v>
-      </c>
-      <c r="AK4">
-        <v>-0.1728723404255319</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>0</v>
-      </c>
-      <c r="AN4">
-        <v>0</v>
-      </c>
-      <c r="AP4">
-        <v>-4.767726161369193</v>
+      <c r="D6">
+        <v>0.03759999999999999</v>
+      </c>
+      <c r="E6">
+        <v>0.0926</v>
+      </c>
+      <c r="G6">
+        <v>0.05903873744619799</v>
+      </c>
+      <c r="H6">
+        <v>0.05903873744619799</v>
+      </c>
+      <c r="I6">
+        <v>0.05939741750358679</v>
+      </c>
+      <c r="J6">
+        <v>0.05750368807494302</v>
+      </c>
+      <c r="K6">
+        <v>8.23</v>
+      </c>
+      <c r="L6">
+        <v>0.05903873744619799</v>
+      </c>
+      <c r="M6">
+        <v>2.7258</v>
+      </c>
+      <c r="N6">
+        <v>0.0238061135371179</v>
+      </c>
+      <c r="O6">
+        <v>0.3312029161603888</v>
+      </c>
+      <c r="P6">
+        <v>2.7258</v>
+      </c>
+      <c r="Q6">
+        <v>0.0238061135371179</v>
+      </c>
+      <c r="R6">
+        <v>0.3312029161603888</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>4.82</v>
+      </c>
+      <c r="V6">
+        <v>0.04209606986899563</v>
+      </c>
+      <c r="W6">
+        <v>0.06220710506424792</v>
+      </c>
+      <c r="X6">
+        <v>0.1541982539165212</v>
+      </c>
+      <c r="Y6">
+        <v>-0.09199114885227327</v>
+      </c>
+      <c r="Z6">
+        <v>1.235815602836879</v>
+      </c>
+      <c r="AA6">
+        <v>0.07106395494367959</v>
+      </c>
+      <c r="AB6">
+        <v>0.1541982539165212</v>
+      </c>
+      <c r="AC6">
+        <v>-0.08313429897284161</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>-4.82</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>-0.04394602479941648</v>
+      </c>
+      <c r="AK6">
+        <v>-0.04030774376986118</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/tunisia/tunisia_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/tunisia/tunisia_insurance_general.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.111</v>
+        <v>0.1</v>
       </c>
       <c r="E2">
-        <v>0.0926</v>
+        <v>0.204</v>
       </c>
       <c r="G2">
-        <v>0.05871375251220212</v>
+        <v>0.03561680492373562</v>
       </c>
       <c r="H2">
-        <v>0.05871375251220212</v>
+        <v>0.03561680492373562</v>
       </c>
       <c r="I2">
-        <v>0.1041343669250646</v>
+        <v>0.118009098207118</v>
       </c>
       <c r="J2">
-        <v>0.08736744492902861</v>
+        <v>0.095554138075265</v>
       </c>
       <c r="K2">
-        <v>30.02</v>
+        <v>31.36</v>
       </c>
       <c r="L2">
-        <v>0.08619006603502727</v>
+        <v>0.08391758094728392</v>
       </c>
       <c r="M2">
-        <v>13.5968</v>
+        <v>9.49</v>
       </c>
       <c r="N2">
-        <v>0.04008490566037736</v>
+        <v>0.02731721358664364</v>
       </c>
       <c r="O2">
-        <v>0.4529247168554297</v>
+        <v>0.3026147959183674</v>
       </c>
       <c r="P2">
-        <v>13.5968</v>
+        <v>9.49</v>
       </c>
       <c r="Q2">
-        <v>0.04008490566037736</v>
+        <v>0.02731721358664364</v>
       </c>
       <c r="R2">
-        <v>0.4529247168554297</v>
+        <v>0.3026147959183674</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>35.69</v>
+        <v>33.71</v>
       </c>
       <c r="V2">
-        <v>0.1052181603773585</v>
+        <v>0.09703511801957398</v>
       </c>
       <c r="W2">
-        <v>0.1618263201768693</v>
+        <v>0.1418292934857457</v>
       </c>
       <c r="X2">
-        <v>0.1541982539165212</v>
+        <v>0.1493946791911214</v>
       </c>
       <c r="Y2">
-        <v>0.007628066260348065</v>
+        <v>-0.007565385705375627</v>
       </c>
       <c r="Z2">
-        <v>1.658832102187487</v>
+        <v>1.695399691498049</v>
       </c>
       <c r="AA2">
-        <v>0.1952190787239407</v>
+        <v>0.2186777364387886</v>
       </c>
       <c r="AB2">
-        <v>0.1541982539165212</v>
+        <v>0.1493946791911214</v>
       </c>
       <c r="AC2">
-        <v>0.04102082480741947</v>
+        <v>0.06928305724766723</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AG2">
-        <v>-35.69</v>
+        <v>-28.86</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>0.01376863023420866</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>0.0163879033620544</v>
       </c>
       <c r="AJ2">
-        <v>-0.1175908536786267</v>
+        <v>-0.09060086645319269</v>
       </c>
       <c r="AK2">
-        <v>-0.1582634916411689</v>
+        <v>-0.1100518608907871</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -693,10 +693,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>0</v>
+        <v>0.314526588845655</v>
       </c>
       <c r="AP2">
-        <v>-2.764523625096824</v>
+        <v>-1.8715953307393</v>
       </c>
     </row>
     <row r="3">
@@ -716,46 +716,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.165</v>
+        <v>0.153</v>
       </c>
       <c r="E3">
-        <v>0.238</v>
+        <v>0.204</v>
       </c>
       <c r="G3">
-        <v>0.1271910112359551</v>
+        <v>0.1291666666666667</v>
       </c>
       <c r="H3">
-        <v>0.1271910112359551</v>
+        <v>0.1291666666666667</v>
       </c>
       <c r="I3">
-        <v>0.1337078651685393</v>
+        <v>0.1310416666666667</v>
       </c>
       <c r="J3">
-        <v>0.1101789007395578</v>
+        <v>0.1001192931793179</v>
       </c>
       <c r="K3">
-        <v>4.87</v>
+        <v>4.63</v>
       </c>
       <c r="L3">
-        <v>0.109438202247191</v>
+        <v>0.09645833333333333</v>
       </c>
       <c r="M3">
-        <v>0.981</v>
+        <v>1.11</v>
       </c>
       <c r="N3">
-        <v>0.02286713286713287</v>
+        <v>0.02624113475177305</v>
       </c>
       <c r="O3">
-        <v>0.2014373716632444</v>
+        <v>0.2397408207343413</v>
       </c>
       <c r="P3">
-        <v>0.981</v>
+        <v>1.11</v>
       </c>
       <c r="Q3">
-        <v>0.02286713286713287</v>
+        <v>0.02624113475177305</v>
       </c>
       <c r="R3">
-        <v>0.2014373716632444</v>
+        <v>0.2397408207343413</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,31 +764,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>19.7</v>
+        <v>22</v>
       </c>
       <c r="V3">
-        <v>0.4592074592074592</v>
+        <v>0.5200945626477542</v>
       </c>
       <c r="W3">
-        <v>0.1940239043824701</v>
+        <v>0.1747169811320755</v>
       </c>
       <c r="X3">
-        <v>0.1541982539165212</v>
+        <v>0.1493946791911214</v>
       </c>
       <c r="Y3">
-        <v>0.03982565046594891</v>
+        <v>0.02532230194095408</v>
       </c>
       <c r="Z3">
-        <v>7.416666666666667</v>
+        <v>7.058823529411764</v>
       </c>
       <c r="AA3">
-        <v>0.8171601804850536</v>
+        <v>0.7067244224422441</v>
       </c>
       <c r="AB3">
-        <v>0.1541982539165212</v>
+        <v>0.1493946791911214</v>
       </c>
       <c r="AC3">
-        <v>0.6629619265685324</v>
+        <v>0.5573297432511227</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -800,7 +800,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-19.7</v>
+        <v>-22</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -809,10 +809,10 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.8491379310344828</v>
+        <v>-1.083743842364532</v>
       </c>
       <c r="AK3">
-        <v>-2.897058823529411</v>
+        <v>-2.75</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -824,7 +824,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-3.213703099510604</v>
+        <v>-3.400309119010819</v>
       </c>
     </row>
     <row r="4">
@@ -850,34 +850,34 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0.1697699890470975</v>
+        <v>0.1650671785028791</v>
       </c>
       <c r="J4">
-        <v>0.1287228615583129</v>
+        <v>0.135767754318618</v>
       </c>
       <c r="K4">
-        <v>9.699999999999999</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="L4">
-        <v>0.1062431544359255</v>
+        <v>0.0946257197696737</v>
       </c>
       <c r="M4">
-        <v>4.46</v>
+        <v>4.51</v>
       </c>
       <c r="N4">
-        <v>0.05492610837438423</v>
+        <v>0.05857142857142857</v>
       </c>
       <c r="O4">
-        <v>0.4597938144329897</v>
+        <v>0.4574036511156186</v>
       </c>
       <c r="P4">
-        <v>4.46</v>
+        <v>4.51</v>
       </c>
       <c r="Q4">
-        <v>0.05492610837438423</v>
+        <v>0.05857142857142857</v>
       </c>
       <c r="R4">
-        <v>0.4597938144329897</v>
+        <v>0.4574036511156186</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -886,31 +886,31 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>6.67</v>
+        <v>4.71</v>
       </c>
       <c r="V4">
-        <v>0.08214285714285714</v>
+        <v>0.06116883116883117</v>
       </c>
       <c r="W4">
-        <v>0.1901960784313725</v>
+        <v>0.1878095238095238</v>
       </c>
       <c r="X4">
-        <v>0.1541982539165212</v>
+        <v>0.1493946791911214</v>
       </c>
       <c r="Y4">
-        <v>0.03599782451485134</v>
+        <v>0.03841484461840242</v>
       </c>
       <c r="Z4">
-        <v>2.213172375342399</v>
+        <v>2.275854537512286</v>
       </c>
       <c r="AA4">
-        <v>0.2848858812758823</v>
+        <v>0.3089876597138801</v>
       </c>
       <c r="AB4">
-        <v>0.1541982539165212</v>
+        <v>0.1493946791911214</v>
       </c>
       <c r="AC4">
-        <v>0.1306876273593611</v>
+        <v>0.1595929805227588</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -922,7 +922,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>-6.67</v>
+        <v>-4.71</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -931,10 +931,10 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.08949416342412451</v>
+        <v>-0.06515423986720155</v>
       </c>
       <c r="AK4">
-        <v>-0.1257778615877805</v>
+        <v>-0.06409035242890189</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -960,46 +960,46 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.111</v>
+        <v>0.1</v>
       </c>
       <c r="E5">
-        <v>0.08710000000000001</v>
+        <v>0.0152</v>
       </c>
       <c r="G5">
-        <v>0.08974008207934336</v>
+        <v>0.09673469387755103</v>
       </c>
       <c r="H5">
-        <v>0.08974008207934336</v>
+        <v>0.09673469387755103</v>
       </c>
       <c r="I5">
-        <v>0.08946648426812587</v>
+        <v>0.1171428571428571</v>
       </c>
       <c r="J5">
-        <v>0.07207300017577514</v>
+        <v>0.0842773989689007</v>
       </c>
       <c r="K5">
-        <v>7.22</v>
+        <v>5.97</v>
       </c>
       <c r="L5">
-        <v>0.0987688098495212</v>
+        <v>0.08122448979591837</v>
       </c>
       <c r="M5">
-        <v>5.43</v>
+        <v>3.87</v>
       </c>
       <c r="N5">
-        <v>0.05397614314115308</v>
+        <v>0.04069400630914827</v>
       </c>
       <c r="O5">
-        <v>0.7520775623268698</v>
+        <v>0.6482412060301508</v>
       </c>
       <c r="P5">
-        <v>5.43</v>
+        <v>3.87</v>
       </c>
       <c r="Q5">
-        <v>0.05397614314115308</v>
+        <v>0.04069400630914827</v>
       </c>
       <c r="R5">
-        <v>0.7520775623268698</v>
+        <v>0.6482412060301508</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1008,31 +1008,31 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>4.5</v>
+        <v>5.48</v>
       </c>
       <c r="V5">
-        <v>0.04473161033797217</v>
+        <v>0.05762355415352262</v>
       </c>
       <c r="W5">
-        <v>0.133456561922366</v>
+        <v>0.1089416058394161</v>
       </c>
       <c r="X5">
-        <v>0.1541982539165212</v>
+        <v>0.1493946791911214</v>
       </c>
       <c r="Y5">
-        <v>-0.02074169199415521</v>
+        <v>-0.04045307335170531</v>
       </c>
       <c r="Z5">
-        <v>1.464518972632928</v>
+        <v>1.523158221945912</v>
       </c>
       <c r="AA5">
-        <v>0.1055522761719991</v>
+        <v>0.1283678131636971</v>
       </c>
       <c r="AB5">
-        <v>0.1541982539165212</v>
+        <v>0.1493946791911214</v>
       </c>
       <c r="AC5">
-        <v>-0.04864597774452213</v>
+        <v>-0.02102686602742432</v>
       </c>
       <c r="AD5">
         <v>0</v>
@@ -1044,7 +1044,7 @@
         <v>0</v>
       </c>
       <c r="AG5">
-        <v>-4.5</v>
+        <v>-5.48</v>
       </c>
       <c r="AH5">
         <v>0</v>
@@ -1053,10 +1053,10 @@
         <v>0</v>
       </c>
       <c r="AJ5">
-        <v>-0.04682622268470343</v>
+        <v>-0.06114706538719037</v>
       </c>
       <c r="AK5">
-        <v>-0.09761388286334056</v>
+        <v>-0.1162988115449915</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1068,7 +1068,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>-0.663716814159292</v>
+        <v>-0.6122905027932962</v>
       </c>
     </row>
     <row r="6">
@@ -1088,103 +1088,100 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.03759999999999999</v>
+        <v>0.0522</v>
       </c>
       <c r="E6">
-        <v>0.0926</v>
+        <v>0.355</v>
       </c>
       <c r="G6">
-        <v>0.05903873744619799</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>0.05903873744619799</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>0.05939741750358679</v>
+        <v>0.08108108108108109</v>
       </c>
       <c r="J6">
-        <v>0.05750368807494302</v>
+        <v>0.07564102564102565</v>
       </c>
       <c r="K6">
-        <v>8.23</v>
+        <v>10.9</v>
       </c>
       <c r="L6">
-        <v>0.05903873744619799</v>
+        <v>0.07364864864864865</v>
       </c>
       <c r="M6">
-        <v>2.7258</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.0238061135371179</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>0.3312029161603888</v>
+        <v>-0</v>
       </c>
       <c r="P6">
-        <v>2.7258</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.0238061135371179</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>0.3312029161603888</v>
+        <v>-0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
-        <v>4.82</v>
+        <v>1.52</v>
       </c>
       <c r="V6">
-        <v>0.04209606986899563</v>
+        <v>0.01142857142857143</v>
       </c>
       <c r="W6">
-        <v>0.06220710506424792</v>
+        <v>0.08762057877813505</v>
       </c>
       <c r="X6">
-        <v>0.1541982539165212</v>
+        <v>0.1528226984765755</v>
       </c>
       <c r="Y6">
-        <v>-0.09199114885227327</v>
+        <v>-0.06520211969844046</v>
       </c>
       <c r="Z6">
-        <v>1.235815602836879</v>
+        <v>1.237665161398227</v>
       </c>
       <c r="AA6">
-        <v>0.07106395494367959</v>
+        <v>0.09361826220832742</v>
       </c>
       <c r="AB6">
-        <v>0.1541982539165212</v>
+        <v>0.1517261705854614</v>
       </c>
       <c r="AC6">
-        <v>-0.08313429897284161</v>
+        <v>-0.05810790837713395</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AG6">
-        <v>-4.82</v>
+        <v>3.33</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>0.03518317011244106</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>0.03588605253422123</v>
       </c>
       <c r="AJ6">
-        <v>-0.04394602479941648</v>
+        <v>0.02442602508618792</v>
       </c>
       <c r="AK6">
-        <v>-0.04030774376986118</v>
+        <v>0.02491955399236698</v>
       </c>
       <c r="AL6">
         <v>0</v>
